--- a/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_crosscorespine[Mod道具信息-CrossCoreSpine].xlsx
+++ b/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_crosscorespine[Mod道具信息-CrossCoreSpine].xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -745,7 +745,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H102" t="n">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H107" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H142" t="n">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H143" t="n">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H145" t="n">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H146" t="n">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H148" t="n">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H149" t="n">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H150" t="n">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H153" t="n">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H154" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H155" t="n">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H156" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H157" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H158" t="n">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H160" t="n">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H161" t="n">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H162" t="n">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H163" t="n">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H164" t="n">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H165" t="n">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H166" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H167" t="n">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H168" t="n">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H169" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H170" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H171" t="n">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H172" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H173" t="n">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H174" t="n">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H175" t="n">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H176" t="n">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H177" t="n">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H178" t="n">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H179" t="n">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H180" t="n">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H181" t="n">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H182" t="n">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H183" t="n">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H184" t="n">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H185" t="n">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H186" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H187" t="n">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H188" t="n">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H189" t="n">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H190" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H191" t="n">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H192" t="n">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H193" t="n">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H194" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H195" t="n">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H196" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H197" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H198" t="n">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H199" t="n">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H200" t="n">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H201" t="n">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H202" t="n">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H203" t="n">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H204" t="n">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H205" t="n">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H206" t="n">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H207" t="n">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H208" t="n">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H209" t="n">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H210" t="n">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H211" t="n">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H212" t="n">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H213" t="n">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H214" t="n">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H215" t="n">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H216" t="n">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H217" t="n">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H218" t="n">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H219" t="n">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H220" t="n">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H221" t="n">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H222" t="n">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H223" t="n">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H224" t="n">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H225" t="n">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H226" t="n">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H227" t="n">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H228" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H229" t="n">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H230" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H231" t="n">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H232" t="n">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H233" t="n">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H234" t="n">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H235" t="n">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H236" t="n">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H237" t="n">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H238" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H239" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H240" t="n">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H241" t="n">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H242" t="n">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H243" t="n">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H244" t="n">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H245" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H246" t="n">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H247" t="n">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H248" t="n">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H249" t="n">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H250" t="n">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H251" t="n">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H252" t="n">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H253" t="n">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H254" t="n">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H255" t="n">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H256" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H257" t="n">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H258" t="n">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H259" t="n">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H260" t="n">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H261" t="n">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H262" t="n">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H263" t="n">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H264" t="n">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H265" t="n">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H266" t="n">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H267" t="n">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H268" t="n">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H269" t="n">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H270" t="n">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H271" t="n">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H272" t="n">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H273" t="n">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H274" t="n">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H275" t="n">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H276" t="n">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H277" t="n">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H278" t="n">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H279" t="n">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H280" t="n">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H281" t="n">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H282" t="n">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H283" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H284" t="n">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H285" t="n">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H286" t="n">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H287" t="n">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H288" t="n">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H289" t="n">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H290" t="n">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H291" t="n">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H292" t="n">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H293" t="n">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H294" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H295" t="n">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H296" t="n">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H297" t="n">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H298" t="n">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H299" t="n">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H300" t="n">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H301" t="n">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H302" t="n">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H303" t="n">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H304" t="n">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H305" t="n">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H306" t="n">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H307" t="n">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H308" t="n">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H309" t="n">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H310" t="n">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H311" t="n">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H312" t="n">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H313" t="n">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H314" t="n">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H315" t="n">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H316" t="n">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H317" t="n">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H318" t="n">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H319" t="n">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H320" t="n">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H321" t="n">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H322" t="n">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H323" t="n">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H324" t="n">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H325" t="n">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H326" t="n">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H327" t="n">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H328" t="n">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H329" t="n">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H330" t="n">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H331" t="n">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H332" t="n">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H333" t="n">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H334" t="n">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H335" t="n">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H336" t="n">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H337" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H338" t="n">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H339" t="n">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H340" t="n">
@@ -16155,7 +16155,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H341" t="n">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H342" t="n">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H343" t="n">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H344" t="n">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H345" t="n">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H346" t="n">
@@ -16431,7 +16431,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H347" t="n">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H348" t="n">
@@ -16523,7 +16523,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H349" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H350" t="n">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H351" t="n">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H352" t="n">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H353" t="n">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H354" t="n">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H355" t="n">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H356" t="n">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H357" t="n">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H358" t="n">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H359" t="n">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H360" t="n">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H361" t="n">
@@ -17121,7 +17121,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H362" t="n">
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H363" t="n">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H364" t="n">
@@ -17259,7 +17259,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H365" t="n">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H366" t="n">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H367" t="n">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H368" t="n">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H369" t="n">
@@ -17489,7 +17489,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H370" t="n">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H371" t="n">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H372" t="n">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H373" t="n">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H374" t="n">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H375" t="n">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H376" t="n">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H377" t="n">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H378" t="n">
@@ -17903,7 +17903,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H379" t="n">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H380" t="n">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H381" t="n">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H382" t="n">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H383" t="n">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H384" t="n">
@@ -18179,7 +18179,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H385" t="n">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H386" t="n">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H387" t="n">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H388" t="n">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H389" t="n">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H390" t="n">
@@ -18455,7 +18455,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H391" t="n">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H392" t="n">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H393" t="n">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H394" t="n">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H395" t="n">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H396" t="n">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H397" t="n">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H398" t="n">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H399" t="n">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H400" t="n">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H401" t="n">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H402" t="n">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H403" t="n">
@@ -19053,7 +19053,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H404" t="n">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H405" t="n">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H406" t="n">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H407" t="n">
@@ -19237,7 +19237,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H408" t="n">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H409" t="n">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H410" t="n">
@@ -19375,7 +19375,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H411" t="n">
@@ -19421,7 +19421,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H412" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H413" t="n">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H414" t="n">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H415" t="n">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H416" t="n">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H417" t="n">
@@ -19697,7 +19697,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H418" t="n">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H419" t="n">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H420" t="n">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H421" t="n">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H422" t="n">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H423" t="n">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H424" t="n">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H425" t="n">
